--- a/data/rio_fragua_chorroso_analysis_data.xlsx
+++ b/data/rio_fragua_chorroso_analysis_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83e1955ea5871ea0/UofG OneDrive Backup 15032025/PhD/Modern Rivers/Article 1/Quantitative analysis of channel characteristics of distributive fluvial systems/Datasets/Río Fragua Chorroso/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83e1955ea5871ea0/UofG OneDrive Backup 15032025/PhD/Modern Rivers/Colombia06River/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2736" documentId="13_ncr:1_{A8A5181B-1864-4B37-B814-6B100885A5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1E6FB14-B074-44B6-A6A0-0ABAD17BD921}"/>
+  <xr:revisionPtr revIDLastSave="2765" documentId="13_ncr:1_{A8A5181B-1864-4B37-B814-6B100885A5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06FED0D8-EF78-4007-B216-D22726F36FAF}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{80361B5F-9A8D-4CB3-A7FB-D490803790DE}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{80361B5F-9A8D-4CB3-A7FB-D490803790DE}"/>
   </bookViews>
   <sheets>
     <sheet name="channel_profile" sheetId="16" r:id="rId1"/>
@@ -40,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
-  <si>
-    <t>segment</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>channelBelt</t>
   </si>
@@ -61,15 +58,6 @@
   </si>
   <si>
     <t>vegetatedBar</t>
-  </si>
-  <si>
-    <t>waterArea</t>
-  </si>
-  <si>
-    <t>sedimentArea</t>
-  </si>
-  <si>
-    <t>vegetationArea</t>
   </si>
   <si>
     <t>area</t>
@@ -107,13 +95,20 @@
   <si>
     <t>environment</t>
   </si>
+  <si>
+    <t>segmentPercent</t>
+  </si>
+  <si>
+    <t>segmentAbsolute</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -248,7 +243,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -272,6 +267,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -609,10 +606,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -30847,52 +30844,55 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5D9C95-28FB-42F4-A5A6-B7CAB53EE7A8}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>0</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="16">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7">
         <v>8.0430000000000001E-2</v>
       </c>
-      <c r="C2" s="6">
+      <c r="D2" s="6">
         <v>8.0430000000000001E-2</v>
-      </c>
-      <c r="D2" s="6">
-        <v>0</v>
       </c>
       <c r="E2" s="6">
         <v>0</v>
@@ -30903,249 +30903,282 @@
       <c r="G2" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>5</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="C3" s="8">
         <v>1.1543099999999999</v>
       </c>
-      <c r="C3" s="6">
+      <c r="D3" s="6">
         <v>5.5508000000000002E-2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="E3" s="6">
         <v>1.0976790000000001</v>
       </c>
-      <c r="E3" s="6">
+      <c r="F3" s="6">
         <v>1.923448</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <v>0.398644</v>
       </c>
-      <c r="G3" s="6">
+      <c r="H3" s="6">
         <v>0.69903499999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>10</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="C4" s="8">
         <v>0.40448400000000001</v>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="6">
         <v>0.25816600000000001</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="6">
         <v>0.146318</v>
       </c>
-      <c r="E4" s="6">
+      <c r="F4" s="6">
         <v>0.55532499999999996</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>0.146318</v>
       </c>
-      <c r="G4" s="6">
+      <c r="H4" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>15</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="15">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C5" s="8">
         <v>2.062665</v>
       </c>
-      <c r="C5" s="6">
+      <c r="D5" s="6">
         <v>0.26294099999999998</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="6">
         <v>1.799725</v>
       </c>
-      <c r="E5" s="6">
+      <c r="F5" s="6">
         <v>4.5604149999999999</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <v>0.32011899999999999</v>
       </c>
-      <c r="G5" s="6">
+      <c r="H5" s="6">
         <v>1.479606</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>20</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="15">
+        <v>27.2</v>
+      </c>
+      <c r="C6" s="8">
         <v>0.25611499999999998</v>
       </c>
-      <c r="C6" s="6">
+      <c r="D6" s="6">
         <v>0.149226</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <v>0.10689</v>
       </c>
-      <c r="E6" s="6">
+      <c r="F6" s="6">
         <v>0.139622</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>0.10689</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>25</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="15">
+        <v>34</v>
+      </c>
+      <c r="C7" s="8">
         <v>2.2203889999999999</v>
       </c>
-      <c r="C7" s="6">
+      <c r="D7" s="6">
         <v>0.209703</v>
       </c>
-      <c r="D7" s="6">
+      <c r="E7" s="6">
         <v>2.0106850000000001</v>
       </c>
-      <c r="E7" s="6">
+      <c r="F7" s="6">
         <v>3.5166390000000001</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>0.208344</v>
       </c>
-      <c r="G7" s="6">
+      <c r="H7" s="6">
         <v>1.802341</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>30</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="15">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C8" s="8">
         <v>0.885015</v>
       </c>
-      <c r="C8" s="6">
+      <c r="D8" s="6">
         <v>0.19639200000000001</v>
       </c>
-      <c r="D8" s="6">
+      <c r="E8" s="6">
         <v>0.68862400000000001</v>
       </c>
-      <c r="E8" s="6">
+      <c r="F8" s="6">
         <v>1.114425</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <v>7.6322000000000001E-2</v>
       </c>
-      <c r="G8" s="6">
+      <c r="H8" s="6">
         <v>0.61230200000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>35</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="15">
+        <v>47.6</v>
+      </c>
+      <c r="C9" s="10">
         <v>0.21584500000000001</v>
       </c>
-      <c r="C9" s="6">
+      <c r="D9" s="6">
         <v>0.166244</v>
       </c>
-      <c r="D9" s="6">
+      <c r="E9" s="6">
         <v>4.9600999999999999E-2</v>
       </c>
-      <c r="E9" s="6">
+      <c r="F9" s="6">
         <v>8.8491E-2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>4.9600999999999999E-2</v>
       </c>
-      <c r="G9" s="6">
+      <c r="H9" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>40</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="15">
+        <v>54.4</v>
+      </c>
+      <c r="C10" s="10">
         <v>0.18881899999999999</v>
       </c>
-      <c r="C10" s="6">
+      <c r="D10" s="6">
         <v>0.166689</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <v>2.2128999999999999E-2</v>
       </c>
-      <c r="E10" s="6">
+      <c r="F10" s="6">
         <v>4.3305000000000003E-2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>2.2128999999999999E-2</v>
       </c>
-      <c r="G10" s="6">
+      <c r="H10" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>45</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="15">
+        <v>61.2</v>
+      </c>
+      <c r="C11" s="10">
         <v>0.236986</v>
       </c>
-      <c r="C11" s="6">
+      <c r="D11" s="6">
         <v>0.14403199999999999</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="6">
         <v>9.2952999999999994E-2</v>
       </c>
-      <c r="E11" s="6">
+      <c r="F11" s="6">
         <v>0.17349300000000001</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <v>9.2952999999999994E-2</v>
       </c>
-      <c r="G11" s="6">
+      <c r="H11" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>50</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="15">
+        <v>68</v>
+      </c>
+      <c r="C12" s="10">
         <v>0.29865700000000001</v>
       </c>
-      <c r="C12" s="6">
+      <c r="D12" s="6">
         <v>0.164214</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="6">
         <v>0.13444400000000001</v>
       </c>
-      <c r="E12" s="6">
+      <c r="F12" s="6">
         <v>0.496332</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <v>8.7016999999999997E-2</v>
       </c>
-      <c r="G12" s="6">
+      <c r="H12" s="6">
         <v>4.7426999999999997E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>55</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="15">
+        <v>74.8</v>
+      </c>
+      <c r="C13" s="10">
         <v>0.29778300000000002</v>
       </c>
-      <c r="C13" s="6">
+      <c r="D13" s="6">
         <v>0.29778300000000002</v>
-      </c>
-      <c r="D13" s="6">
-        <v>0</v>
       </c>
       <c r="E13" s="6">
         <v>0</v>
@@ -31156,111 +31189,126 @@
       <c r="G13" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H13" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>60</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="15">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C14" s="10">
         <v>0.37029699999999999</v>
       </c>
-      <c r="C14" s="6">
+      <c r="D14" s="6">
         <v>0.177566</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>0.19273100000000001</v>
       </c>
-      <c r="E14" s="6">
+      <c r="F14" s="6">
         <v>0.26334999999999997</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>0.19273100000000001</v>
       </c>
-      <c r="G14" s="6">
+      <c r="H14" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>65</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="15">
+        <v>88.4</v>
+      </c>
+      <c r="C15" s="10">
         <v>0.67698199999999997</v>
       </c>
-      <c r="C15" s="6">
+      <c r="D15" s="6">
         <v>0.28645300000000001</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>0.39052900000000002</v>
       </c>
-      <c r="E15" s="6">
+      <c r="F15" s="6">
         <v>0.43226300000000001</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>0.19295799999999999</v>
       </c>
-      <c r="G15" s="6">
+      <c r="H15" s="6">
         <v>0.197572</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>70</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="15">
+        <v>95.2</v>
+      </c>
+      <c r="C16" s="12">
         <v>0.48053600000000002</v>
       </c>
-      <c r="C16" s="6">
+      <c r="D16" s="6">
         <v>0.30912200000000001</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <v>0.17141400000000001</v>
       </c>
-      <c r="E16" s="6">
+      <c r="F16" s="6">
         <v>0.29555300000000001</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <v>5.3628000000000002E-2</v>
       </c>
-      <c r="G16" s="6">
+      <c r="H16" s="6">
         <v>0.117786</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>75</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="15">
+        <v>102</v>
+      </c>
+      <c r="C17" s="12">
         <v>0.37776100000000001</v>
       </c>
-      <c r="C17" s="6">
+      <c r="D17" s="6">
         <v>0.17579700000000001</v>
       </c>
-      <c r="D17" s="6">
+      <c r="E17" s="6">
         <v>0.201964</v>
       </c>
-      <c r="E17" s="6">
+      <c r="F17" s="6">
         <v>0.30422100000000002</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>0.201964</v>
       </c>
-      <c r="G17" s="6">
+      <c r="H17" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>80</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="15">
+        <v>108.8</v>
+      </c>
+      <c r="C18" s="12">
         <v>0.42868400000000001</v>
       </c>
-      <c r="C18" s="6">
+      <c r="D18" s="6">
         <v>0.42868400000000001</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0</v>
       </c>
       <c r="E18" s="6">
         <v>0</v>
@@ -31271,42 +31319,48 @@
       <c r="G18" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H18" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>85</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="15">
+        <v>115.6</v>
+      </c>
+      <c r="C19" s="12">
         <v>0.33096700000000001</v>
       </c>
-      <c r="C19" s="6">
+      <c r="D19" s="6">
         <v>0.18169399999999999</v>
       </c>
-      <c r="D19" s="6">
+      <c r="E19" s="6">
         <v>0.14927399999999999</v>
       </c>
-      <c r="E19" s="6">
+      <c r="F19" s="6">
         <v>0.19483300000000001</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <v>0.14927399999999999</v>
       </c>
-      <c r="G19" s="6">
+      <c r="H19" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>90</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="15">
+        <v>122.4</v>
+      </c>
+      <c r="C20" s="12">
         <v>0.32146400000000003</v>
       </c>
-      <c r="C20" s="6">
+      <c r="D20" s="6">
         <v>0.32146400000000003</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0</v>
       </c>
       <c r="E20" s="6">
         <v>0</v>
@@ -31317,50 +31371,59 @@
       <c r="G20" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>95</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="15">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="C21" s="12">
         <v>0.67697799999999997</v>
       </c>
-      <c r="C21" s="6">
+      <c r="D21" s="6">
         <v>0.381027</v>
       </c>
-      <c r="D21" s="6">
+      <c r="E21" s="6">
         <v>0.29594999999999999</v>
       </c>
-      <c r="E21" s="6">
+      <c r="F21" s="6">
         <v>0.518343</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <v>0.11205900000000001</v>
       </c>
-      <c r="G21" s="6">
+      <c r="H21" s="6">
         <v>0.183891</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>100</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="15">
+        <v>136</v>
+      </c>
+      <c r="C22" s="11">
         <v>0.66610599999999998</v>
       </c>
-      <c r="C22" s="6">
+      <c r="D22" s="6">
         <v>0.43649300000000002</v>
       </c>
-      <c r="D22" s="6">
+      <c r="E22" s="6">
         <v>0.22961500000000001</v>
       </c>
-      <c r="E22" s="6">
+      <c r="F22" s="6">
         <v>0.34199800000000002</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <v>0.22961500000000001</v>
       </c>
-      <c r="G22" s="6">
+      <c r="H22" s="6">
         <v>0</v>
       </c>
     </row>
@@ -31372,353 +31435,414 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594816B0-6BAF-494C-B256-ACA7C51AE768}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>7</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="15">
+        <v>6.8</v>
+      </c>
+      <c r="C2" s="2">
         <v>0.79982600000000004</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>2.5496379999999998</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>4.069242</v>
       </c>
-      <c r="E2" s="14">
+      <c r="F2" s="14">
         <v>6.6188799999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>10</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="15">
+        <v>13.6</v>
+      </c>
+      <c r="C3" s="2">
         <v>1.1645099999999999</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="2">
         <v>1.553758</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="2">
         <v>3.3973149999999999</v>
       </c>
-      <c r="E3" s="14">
+      <c r="F3" s="14">
         <v>4.9510730000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>15</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="15">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="C4" s="2">
         <v>1.5826359999999999</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="2">
         <v>1.7043379999999999</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="2">
         <v>8.8139190000000003</v>
       </c>
-      <c r="E4" s="14">
+      <c r="F4" s="14">
         <v>10.518257</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>20</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="15">
+        <v>27.2</v>
+      </c>
+      <c r="C5" s="2">
         <v>1.5136689999999999</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="2">
         <v>1.384757</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="2">
         <v>4.1122820000000004</v>
       </c>
-      <c r="E5" s="14">
+      <c r="F5" s="14">
         <v>5.4970390000000009</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>25</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="15">
+        <v>34</v>
+      </c>
+      <c r="C6" s="2">
         <v>1.8244039999999999</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="2">
         <v>1.6210899999999999</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>6.4381680000000001</v>
       </c>
-      <c r="E6" s="14">
+      <c r="F6" s="14">
         <v>8.0592579999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>30</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="15">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="C7" s="2">
         <v>1.1665380000000001</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="2">
         <v>0.83082599999999995</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>1.4559930000000001</v>
       </c>
-      <c r="E7" s="14">
+      <c r="F7" s="14">
         <v>2.2868189999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>35</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="15">
+        <v>47.6</v>
+      </c>
+      <c r="C8" s="2">
         <v>1.059517</v>
       </c>
-      <c r="C8" s="2">
+      <c r="D8" s="2">
         <v>0.51332299999999997</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>0.28055999999999998</v>
       </c>
-      <c r="E8" s="14">
+      <c r="F8" s="14">
         <v>0.79388299999999989</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>40</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="15">
+        <v>54.4</v>
+      </c>
+      <c r="C9" s="2">
         <v>1.051272</v>
       </c>
-      <c r="C9" s="2">
+      <c r="D9" s="2">
         <v>0.35637400000000002</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>1.8377000000000001E-2</v>
       </c>
-      <c r="E9" s="14">
+      <c r="F9" s="14">
         <v>0.374751</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>45</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="15">
+        <v>61.2</v>
+      </c>
+      <c r="C10" s="2">
         <v>0.99168400000000001</v>
       </c>
-      <c r="C10" s="2">
+      <c r="D10" s="2">
         <v>0.39905200000000002</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>4.1119999999999997E-2</v>
       </c>
-      <c r="E10" s="14">
+      <c r="F10" s="14">
         <v>0.44017200000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>50</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="15">
+        <v>68</v>
+      </c>
+      <c r="C11" s="2">
         <v>1.0398780000000001</v>
       </c>
-      <c r="C11" s="2">
+      <c r="D11" s="2">
         <v>0.19930100000000001</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>0.27074300000000001</v>
       </c>
-      <c r="E11" s="14">
+      <c r="F11" s="14">
         <v>0.47004400000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>55</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="15">
+        <v>74.8</v>
+      </c>
+      <c r="C12" s="2">
         <v>1.5814820000000001</v>
       </c>
-      <c r="C12" s="2">
+      <c r="D12" s="2">
         <v>0.29488900000000001</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>1.196637</v>
       </c>
-      <c r="E12" s="14">
+      <c r="F12" s="14">
         <v>1.4915259999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>60</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="15">
+        <v>81.599999999999994</v>
+      </c>
+      <c r="C13" s="2">
         <v>1.333655</v>
       </c>
-      <c r="C13" s="2">
+      <c r="D13" s="2">
         <v>0.675539</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>9.8156999999999994E-2</v>
       </c>
-      <c r="E13" s="14">
+      <c r="F13" s="14">
         <v>0.77369599999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>65</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="15">
+        <v>88.4</v>
+      </c>
+      <c r="C14" s="2">
         <v>1.4329769999999999</v>
       </c>
-      <c r="C14" s="2">
+      <c r="D14" s="2">
         <v>0.66742299999999999</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>0.121533</v>
       </c>
-      <c r="E14" s="14">
+      <c r="F14" s="14">
         <v>0.78895599999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>70</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="15">
+        <v>95.2</v>
+      </c>
+      <c r="C15" s="2">
         <v>1.6591750000000001</v>
       </c>
-      <c r="C15" s="2">
+      <c r="D15" s="2">
         <v>0.29776999999999998</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>0.17317099999999999</v>
       </c>
-      <c r="E15" s="14">
+      <c r="F15" s="14">
         <v>0.47094099999999994</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>75</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="15">
+        <v>102</v>
+      </c>
+      <c r="C16" s="2">
         <v>2.0792869999999999</v>
       </c>
-      <c r="C16" s="2">
+      <c r="D16" s="2">
         <v>0.97730499999999998</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>0.46448200000000001</v>
       </c>
-      <c r="E16" s="14">
+      <c r="F16" s="14">
         <v>1.4417869999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>80</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="15">
+        <v>108.8</v>
+      </c>
+      <c r="C17" s="2">
         <v>1.9320269999999999</v>
       </c>
-      <c r="C17" s="2">
+      <c r="D17" s="2">
         <v>0.51466000000000001</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>0.109749</v>
       </c>
-      <c r="E17" s="14">
+      <c r="F17" s="14">
         <v>0.62440899999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>85</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="15">
+        <v>115.6</v>
+      </c>
+      <c r="C18" s="2">
         <v>1.5373349999999999</v>
       </c>
-      <c r="C18" s="2">
+      <c r="D18" s="2">
         <v>0.77288100000000004</v>
       </c>
-      <c r="D18" s="2">
+      <c r="E18" s="2">
         <v>0.470192</v>
       </c>
-      <c r="E18" s="14">
+      <c r="F18" s="14">
         <v>1.2430730000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>90</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="15">
+        <v>122.4</v>
+      </c>
+      <c r="C19" s="2">
         <v>2.2415180000000001</v>
       </c>
-      <c r="C19" s="2">
+      <c r="D19" s="2">
         <v>1.195676</v>
       </c>
-      <c r="D19" s="2">
+      <c r="E19" s="2">
         <v>1.511657</v>
       </c>
-      <c r="E19" s="14">
+      <c r="F19" s="14">
         <v>2.7073330000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>95</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="15">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="C20" s="2">
         <v>2.4595799999999999</v>
       </c>
-      <c r="C20" s="2">
+      <c r="D20" s="2">
         <v>0.930844</v>
       </c>
-      <c r="D20" s="2">
+      <c r="E20" s="2">
         <v>1.1375029999999999</v>
       </c>
-      <c r="E20" s="14">
+      <c r="F20" s="14">
         <v>2.0683470000000002</v>
       </c>
     </row>
@@ -31739,15 +31863,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2">
         <f>SUM(domain_scale!B2:B4)</f>
@@ -31756,7 +31880,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2">
         <f>SUM(domain_scale!C2:C4)</f>
@@ -31765,7 +31889,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(domain_scale!D2:D4)</f>
@@ -31783,28 +31907,28 @@
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2">
         <v>8.3947880000000001</v>
@@ -31818,7 +31942,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
         <v>8.0430469999999996</v>
@@ -31832,7 +31956,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
         <v>13.424509</v>
